--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,6 +1240,1053 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129503782</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>589623</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6932819</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129503534</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västra kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>589526</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6932849</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129504304</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>589712</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6932700</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129503601</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>589565</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6932882</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129503763</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>589605</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6932826</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129505836</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98716</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>589494</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6932939</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129504648</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>589757</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6932765</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129503457</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Västra kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>589451</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6932898</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129503676</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57831</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>589566</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6932896</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129503737</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91513</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>589606</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6932848</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1242,7 +1242,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129503782</v>
+        <v>129503534</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1278,14 +1278,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589623</v>
+        <v>589526</v>
       </c>
       <c r="R7" t="n">
-        <v>6932819</v>
+        <v>6932849</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129503534</v>
+        <v>129503782</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1385,14 +1385,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589526</v>
+        <v>589623</v>
       </c>
       <c r="R8" t="n">
-        <v>6932849</v>
+        <v>6932819</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129503601</v>
+        <v>129503763</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1586,14 +1586,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1602,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589565</v>
+        <v>589605</v>
       </c>
       <c r="R10" t="n">
-        <v>6932882</v>
+        <v>6932826</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,6 +1634,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129503763</v>
+        <v>129503601</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1692,10 +1693,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1704,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589605</v>
+        <v>589565</v>
       </c>
       <c r="R11" t="n">
-        <v>6932826</v>
+        <v>6932882</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,11 +1745,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,7 +1774,7 @@
         <v>129505836</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129503737</v>
       </c>
       <c r="B16" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1242,7 +1242,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129503534</v>
+        <v>129503782</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1278,14 +1278,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589526</v>
+        <v>589623</v>
       </c>
       <c r="R7" t="n">
-        <v>6932849</v>
+        <v>6932819</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129503782</v>
+        <v>129503534</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1385,14 +1385,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589623</v>
+        <v>589526</v>
       </c>
       <c r="R8" t="n">
-        <v>6932819</v>
+        <v>6932849</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129503763</v>
+        <v>129503601</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1586,10 +1586,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1598,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589605</v>
+        <v>589565</v>
       </c>
       <c r="R10" t="n">
-        <v>6932826</v>
+        <v>6932882</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,11 +1638,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,7 +1664,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129503601</v>
+        <v>129503763</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1693,14 +1692,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1709,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589565</v>
+        <v>589605</v>
       </c>
       <c r="R11" t="n">
-        <v>6932882</v>
+        <v>6932826</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,6 +1740,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1774,7 +1774,7 @@
         <v>129505836</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129503737</v>
       </c>
       <c r="B16" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1242,7 +1242,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129503782</v>
+        <v>129503534</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1278,14 +1278,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589623</v>
+        <v>589526</v>
       </c>
       <c r="R7" t="n">
-        <v>6932819</v>
+        <v>6932849</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129503534</v>
+        <v>129503782</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1385,14 +1385,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589526</v>
+        <v>589623</v>
       </c>
       <c r="R8" t="n">
-        <v>6932849</v>
+        <v>6932819</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129503601</v>
+        <v>129503763</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1586,14 +1586,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1602,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589565</v>
+        <v>589605</v>
       </c>
       <c r="R10" t="n">
-        <v>6932882</v>
+        <v>6932826</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,6 +1634,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129503763</v>
+        <v>129503601</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1692,10 +1693,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1704,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589605</v>
+        <v>589565</v>
       </c>
       <c r="R11" t="n">
-        <v>6932826</v>
+        <v>6932882</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,11 +1745,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1242,7 +1242,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129503782</v>
+        <v>129503534</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1278,14 +1278,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589623</v>
+        <v>589526</v>
       </c>
       <c r="R7" t="n">
-        <v>6932819</v>
+        <v>6932849</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129503534</v>
+        <v>129503782</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1385,14 +1385,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589526</v>
+        <v>589623</v>
       </c>
       <c r="R8" t="n">
-        <v>6932849</v>
+        <v>6932819</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129503534</v>
+        <v>129503782</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,14 +1278,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589526</v>
+        <v>589623</v>
       </c>
       <c r="R7" t="n">
-        <v>6932849</v>
+        <v>6932819</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129503782</v>
+        <v>129503534</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,14 +1385,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589623</v>
+        <v>589526</v>
       </c>
       <c r="R8" t="n">
-        <v>6932819</v>
+        <v>6932849</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
         <v>129504304</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129503601</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>129503763</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>129505836</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>129504648</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>129503457</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>129503676</v>
       </c>
       <c r="B15" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>129503737</v>
       </c>
       <c r="B16" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>129503782</v>
       </c>
       <c r="B7" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>129503534</v>
       </c>
       <c r="B8" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129504304</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129503601</v>
+        <v>129503763</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,14 +1586,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1602,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589565</v>
+        <v>589605</v>
       </c>
       <c r="R10" t="n">
-        <v>6932882</v>
+        <v>6932826</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,6 +1634,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,38 +1665,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129503763</v>
+        <v>129505836</v>
       </c>
       <c r="B11" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589605</v>
+        <v>589494</v>
       </c>
       <c r="R11" t="n">
-        <v>6932826</v>
+        <v>6932939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,11 +1740,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,37 +1766,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129505836</v>
+        <v>129504648</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1810,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589494</v>
+        <v>589757</v>
       </c>
       <c r="R12" t="n">
-        <v>6932939</v>
+        <v>6932765</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,6 +1842,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129504648</v>
+        <v>129503457</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,19 +1904,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589757</v>
+        <v>589451</v>
       </c>
       <c r="R13" t="n">
-        <v>6932765</v>
+        <v>6932898</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,50 +1980,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129503457</v>
+        <v>129503737</v>
       </c>
       <c r="B14" t="n">
-        <v>57730</v>
+        <v>91551</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589451</v>
+        <v>589606</v>
       </c>
       <c r="R14" t="n">
-        <v>6932898</v>
+        <v>6932848</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,11 +2051,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,27 +2077,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129503676</v>
+        <v>129503601</v>
       </c>
       <c r="B15" t="n">
-        <v>57834</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2116,12 +2107,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2130,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589566</v>
+        <v>589565</v>
       </c>
       <c r="R15" t="n">
-        <v>6932896</v>
+        <v>6932882</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129503737</v>
+        <v>129503676</v>
       </c>
       <c r="B16" t="n">
-        <v>91545</v>
+        <v>57839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,34 +2194,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589606</v>
+        <v>589566</v>
       </c>
       <c r="R16" t="n">
-        <v>6932848</v>
+        <v>6932896</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,6 +2266,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fick dålig video på dem, men jag såg klart och tydligt att det var lavskrikor.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129503782</v>
+        <v>129504304</v>
       </c>
       <c r="B7" t="n">
-        <v>57735</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,16 +1253,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589623</v>
+        <v>589712</v>
       </c>
       <c r="R7" t="n">
-        <v>6932819</v>
+        <v>6932700</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,11 +1318,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,50 +1344,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129503534</v>
+        <v>129505836</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589526</v>
+        <v>589494</v>
       </c>
       <c r="R8" t="n">
-        <v>6932849</v>
+        <v>6932939</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,11 +1419,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,50 +1445,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129504304</v>
+        <v>129503737</v>
       </c>
       <c r="B9" t="n">
-        <v>57732</v>
+        <v>91552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589712</v>
+        <v>589606</v>
       </c>
       <c r="R9" t="n">
-        <v>6932700</v>
+        <v>6932848</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,27 +1542,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129503763</v>
+        <v>129503676</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57840</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1586,22 +1570,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589605</v>
+        <v>589566</v>
       </c>
       <c r="R10" t="n">
-        <v>6932826</v>
+        <v>6932896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Fick dålig video på dem, men jag såg klart och tydligt att det var lavskrikor.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,37 +1656,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129505836</v>
+        <v>129503782</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1704,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589494</v>
+        <v>589623</v>
       </c>
       <c r="R11" t="n">
-        <v>6932939</v>
+        <v>6932819</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,6 +1732,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129504648</v>
+        <v>129503534</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,19 +1794,19 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589757</v>
+        <v>589526</v>
       </c>
       <c r="R12" t="n">
-        <v>6932765</v>
+        <v>6932849</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129503457</v>
+        <v>129503601</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,22 +1898,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589451</v>
+        <v>589565</v>
       </c>
       <c r="R13" t="n">
-        <v>6932898</v>
+        <v>6932882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,11 +1950,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1980,45 +1976,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129503737</v>
+        <v>129503763</v>
       </c>
       <c r="B14" t="n">
-        <v>91551</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589606</v>
+        <v>589605</v>
       </c>
       <c r="R14" t="n">
-        <v>6932848</v>
+        <v>6932826</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,6 +2052,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129503601</v>
+        <v>129504648</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,14 +2111,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2121,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589565</v>
+        <v>589757</v>
       </c>
       <c r="R15" t="n">
-        <v>6932882</v>
+        <v>6932765</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,6 +2159,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,27 +2190,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129503676</v>
+        <v>129503457</v>
       </c>
       <c r="B16" t="n">
-        <v>57839</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2211,29 +2218,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589566</v>
+        <v>589451</v>
       </c>
       <c r="R16" t="n">
-        <v>6932896</v>
+        <v>6932898</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Fick dålig video på dem, men jag såg klart och tydligt att det var lavskrikor.</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1347,7 +1347,7 @@
         <v>129505836</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>129503737</v>
       </c>
       <c r="B9" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1347,7 +1347,7 @@
         <v>129505836</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>129503737</v>
       </c>
       <c r="B9" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1347,7 +1347,7 @@
         <v>129505836</v>
       </c>
       <c r="B8" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>129503737</v>
       </c>
       <c r="B9" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1347,7 +1347,7 @@
         <v>129505836</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1870,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129503601</v>
+        <v>129503763</v>
       </c>
       <c r="B13" t="n">
         <v>57736</v>
@@ -1898,14 +1898,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1914,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589565</v>
+        <v>589605</v>
       </c>
       <c r="R13" t="n">
-        <v>6932882</v>
+        <v>6932826</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,6 +1946,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1976,7 +1977,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129503763</v>
+        <v>129503601</v>
       </c>
       <c r="B14" t="n">
         <v>57736</v>
@@ -2004,10 +2005,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2016,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589605</v>
+        <v>589565</v>
       </c>
       <c r="R14" t="n">
-        <v>6932826</v>
+        <v>6932882</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,11 +2057,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1659,7 +1659,7 @@
         <v>129503782</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>129503534</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129503763</v>
+        <v>129503601</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1898,10 +1898,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1910,10 +1914,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589605</v>
+        <v>589565</v>
       </c>
       <c r="R13" t="n">
-        <v>6932826</v>
+        <v>6932882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,11 +1950,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,10 +1976,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129503601</v>
+        <v>129503763</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,14 +2004,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2021,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589565</v>
+        <v>589605</v>
       </c>
       <c r="R14" t="n">
-        <v>6932882</v>
+        <v>6932826</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,6 +2052,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,7 +2086,7 @@
         <v>129504648</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>129503457</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -1545,7 +1545,7 @@
         <v>129503676</v>
       </c>
       <c r="B10" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124068463</v>
+        <v>129505777</v>
       </c>
       <c r="B2" t="n">
-        <v>56725</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orre, Mpd</t>
+          <t>Talltita, Västra Kolgården  Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589559</v>
+        <v>589570</v>
       </c>
       <c r="R2" t="n">
-        <v>6932909</v>
+        <v>6932942</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124068269</v>
+        <v>129503737</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Järpe, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589512</v>
+        <v>589606</v>
       </c>
       <c r="R3" t="n">
-        <v>6932934</v>
+        <v>6932848</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,32 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Dropping</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124739409</v>
+        <v>124740983</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589491</v>
+        <v>589413</v>
       </c>
       <c r="R4" t="n">
-        <v>6932910</v>
+        <v>6932907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +939,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +949,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,11 +979,11 @@
         <v>124740035</v>
       </c>
       <c r="B5" t="n">
-        <v>57681</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1118,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124739884</v>
+        <v>129504304</v>
       </c>
       <c r="B6" t="n">
-        <v>56836</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,46 +1099,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Näverbäcken , Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589510</v>
+        <v>589712</v>
       </c>
       <c r="R6" t="n">
-        <v>6932901</v>
+        <v>6932700</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,27 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Alternativ grop av tjäder.</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129504304</v>
+        <v>129503457</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,16 +1201,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1278,14 +1226,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589712</v>
+        <v>589451</v>
       </c>
       <c r="R7" t="n">
-        <v>6932700</v>
+        <v>6932898</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,49 +1297,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129505836</v>
+        <v>129503534</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589494</v>
+        <v>589526</v>
       </c>
       <c r="R8" t="n">
-        <v>6932939</v>
+        <v>6932849</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,45 +1404,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129503737</v>
+        <v>129503601</v>
       </c>
       <c r="B9" t="n">
-        <v>91563</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589606</v>
+        <v>589565</v>
       </c>
       <c r="R9" t="n">
-        <v>6932848</v>
+        <v>6932882</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,27 +1510,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129503676</v>
+        <v>129503763</v>
       </c>
       <c r="B10" t="n">
-        <v>57844</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1570,29 +1538,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589566</v>
+        <v>589605</v>
       </c>
       <c r="R10" t="n">
-        <v>6932896</v>
+        <v>6932826</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1590,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fick dålig video på dem, men jag såg klart och tydligt att det var lavskrikor.</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,7 +1620,7 @@
         <v>129503782</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129503534</v>
+        <v>129504648</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,19 +1755,19 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589526</v>
+        <v>589757</v>
       </c>
       <c r="R12" t="n">
-        <v>6932849</v>
+        <v>6932765</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,54 +1831,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129503601</v>
+        <v>124069531</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589565</v>
+        <v>589493</v>
       </c>
       <c r="R13" t="n">
-        <v>6932882</v>
+        <v>6932974</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,12 +1911,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Skrämde upp den bakom en låga. Hona.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,62 +1946,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129503763</v>
+        <v>124069676</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Spillning tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589605</v>
+        <v>589496</v>
       </c>
       <c r="R14" t="n">
-        <v>6932826</v>
+        <v>6932984</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,17 +2023,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,62 +2053,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129504648</v>
+        <v>124739884</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken , Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589757</v>
+        <v>589510</v>
       </c>
       <c r="R15" t="n">
-        <v>6932765</v>
+        <v>6932901</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,17 +2142,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Alternativ grop av tjäder.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,62 +2177,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129503457</v>
+        <v>124069769</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>44177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Jättesvampmal , Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589451</v>
+        <v>589492</v>
       </c>
       <c r="R16" t="n">
-        <v>6932898</v>
+        <v>6932983</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,17 +2254,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,15 +2284,656 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124068269</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Järpe, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>589512</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6932934</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124068463</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Orre, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>589559</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6932909</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124067954</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Talltita, Västra Kolgården  Sättna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>589570</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6932942</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Lyckades inte fånga dom på video men ljudet fick jag med i alla fall.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129503676</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>589566</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6932896</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fick dålig video på dem, men jag såg klart och tydligt att det var lavskrikor.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124739409</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Näverbäcken , Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>589491</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6932910</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129505836</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>589494</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6932939</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50910-2025 artfynd.xlsx
+++ b/artfynd/A 50910-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505777</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129503737</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124740983</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124740035</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129503457</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129503534</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129503601</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129503763</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1619,6 +1664,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129503782</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1746,6 +1796,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124069531</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1853,6 +1908,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124069676</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1977,6 +2037,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124739884</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2084,6 +2149,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124069769</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2191,6 +2261,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124068269</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2293,6 +2368,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124068463</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2403,6 +2483,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124067954</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2517,6 +2602,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129503676</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2624,6 +2714,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124739409</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2725,6 +2820,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505836</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2827,6 +2927,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129504304</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2934,8 +3039,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129504648</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>